--- a/Test_Files/TestSet-0001.xlsx
+++ b/Test_Files/TestSet-0001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Test Plan" sheetId="1" state="visible" r:id="rId3"/>
@@ -18,12 +18,13 @@
     <sheet name="Regression_Testing" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Compatibility_Testing!$B$7:$J$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Functional_Testing!$B$7:$K$27</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Performance_Testing!$B$7:$J$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Regression_Testing!$B$7:$J$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Security_Testing!$B$7:$J$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">UI_UX_Testing!$B$7:$J$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Compatibility_Testing!$B$7:$K$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Functional_Testing!$B$7:$L$55</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Performance_Testing!$B$7:$K$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Regression_Testing!$B$7:$K$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Security_Testing!$B$7:$K$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Scenarios'!$A$9:$G$23</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">UI_UX_Testing!$B$7:$K$7</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="243">
   <si>
     <t xml:space="preserve">Test Plan</t>
   </si>
@@ -247,6 +248,33 @@
     <t xml:space="preserve">Input fields should reject SQL injection attempts</t>
   </si>
   <si>
+    <t xml:space="preserve">SC-0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure the time it takes for the website to fully load under normal network conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Determine how the website responds when a high number of concurrent users access the homepage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluate how well the website scales when traffic increases over time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0014</t>
+  </si>
+  <si>
     <t xml:space="preserve">Test Suite ID</t>
   </si>
   <si>
@@ -292,27 +320,9 @@
     <t xml:space="preserve">Navigate to the Base URL</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">- Browser: MS Edge
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">- Version: 133.0.3065.51 (Official build) (64-bit)
+    <t xml:space="preserve">- Browser: MS Edge
+- Version: 133.0.3065.51 (Official build) (64-bit)
 - Platform: Windows 10 Pro x64</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">1. Navigate to the Base URL</t>
@@ -324,27 +334,9 @@
     <t xml:space="preserve">TC-0002</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">- Browser: Mozilla Firefox
+    <t xml:space="preserve">- Browser: Mozilla Firefox
 - Version: 135.0 (64-bit)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">- Platform: Windows 10 Pro x64</t>
-    </r>
+- Platform: Windows 10 Pro x64</t>
   </si>
   <si>
     <t xml:space="preserve">TC-0003</t>
@@ -361,28 +353,10 @@
     <t xml:space="preserve">Clicking on the chat client opens the chat box</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">- Browser: MS Edge
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">- Version: 133.0.3065.51 (Official build) (64-bit)
+    <t xml:space="preserve">- Browser: MS Edge
+- Version: 133.0.3065.51 (Official build) (64-bit)
 - Platform: Windows 10 Pro x64
 - The landing page is open and loaded</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">1. The chat client is visible
@@ -402,28 +376,10 @@
     <t xml:space="preserve">TC-0005</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">- Browser: Mozilla Firefox
+    <t xml:space="preserve">- Browser: Mozilla Firefox
 - Version: 135.0 (64-bit)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">- Platform: Windows 10 Pro x64
+- Platform: Windows 10 Pro x64
 - The landing page is open and loaded</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">1. The chat client is displayed as an error
@@ -436,28 +392,10 @@
     <t xml:space="preserve">TC-0006</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">- Browser: Google Chrome
+    <t xml:space="preserve">- Browser: Google Chrome
 - Version: 133.0.6943.60 (Official Build) (64-bit)
 - Platform: Windows 10 Pro x64
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">- The landing page is open and loaded</t>
-    </r>
+- The landing page is open and loaded</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -478,30 +416,12 @@
 - The main menu is available</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1. Click the “Home” link
-2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Click the “Testimonials” link
+    <t xml:space="preserve">1. Click the “Home” link
+2. Click the “Testimonials” link
 3.  Click the site logo
 4.  Click the “Contact” link
 5. Click the site logo
 6. Click the Book Appointment button</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">1. Clicking the “Home” remains on the landing page
@@ -511,13 +431,6 @@
 5. Clicking the “Book Appointment” button takes to the appointment booking page</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Clicking the “Home” remains on the landing page
-2. Clicking “Testimonials” takes to the Testimonials page
-3. Clicking the site logo takes to the landing page
-4. Clicking “Contact” takes to the Contact page
-5. Clicking the “Book Appointment” button takes to the appointment booking page</t>
-  </si>
-  <si>
     <t xml:space="preserve">TC-0008</t>
   </si>
   <si>
@@ -531,9 +444,32 @@
     <t xml:space="preserve">TC-0009</t>
   </si>
   <si>
+    <t xml:space="preserve">The main menu is available and links there are redirecting to the respective page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Browser: Google Chrome
+- Version: 133.0.6943.60 (Official Build) (64-bit)
+- Platform: Windows 10 Pro x64
+- The landing page is open and loaded
+- The main menu is available</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-0010</t>
   </si>
   <si>
+    <t xml:space="preserve">Footer is available and links are working upon clicking on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Scroll down to the footer
+2. Click “Home” link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clicking the “Home” link remains on the landing page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Clicking the “Home” link remains on the landing page</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-0011</t>
   </si>
   <si>
@@ -543,6 +479,17 @@
     <t xml:space="preserve">TC-0013</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Scroll down to the footer
+2. Click “About Us” link
+3. Wait until the about page opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clicking the “About Us” link takes to the about page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clicking the “About Us” link gives 404 error</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-0014</t>
   </si>
   <si>
@@ -552,6 +499,17 @@
     <t xml:space="preserve">TC-0016</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Scroll down to the footer
+2. Click “Testimonials” link
+3. Wait until the testimonials page opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clicking the “Testimonials” link takes to the testimonials page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Clicking the “Testimonials” link takes to the testimonials page</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-0017</t>
   </si>
   <si>
@@ -561,9 +519,236 @@
     <t xml:space="preserve">TC-0019</t>
   </si>
   <si>
+    <t xml:space="preserve">Verify all fields are present and editable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Browser: MS Edge
+- Version: 133.0.3065.51 (Official build) (64-bit)
+- Platform: Windows 10 Pro x64
+- The contact page is open and loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Check if all fields (Name, Email, Phone Number, Country, Address, Message) are present.
+2. Attempt to enter data into each field.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All fields should be present and editable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All fields are present and editable</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-0020</t>
   </si>
   <si>
+    <t xml:space="preserve">- Browser: Mozilla Firefox
+- Version: 135.0 (64-bit)
+- Platform: Windows 10 Pro x64
+- The contact page is open and loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Browser: Google Chrome
+- Version: 133.0.6943.60 (Official Build) (64-bit)
+- Platform: Windows 10 Pro x64
+- The contact page is open and loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify form submission with valid data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter valid data in all fields:
+- Name: "John Doe"
+- Email: "johndoe@example.com"
+- Phone Number: "1234567890"
+- Country: "United States"
+- Address: "123 Main St"
+- Message: "This is a test message."
+2. Click the "Submit Now" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form should submit successfully, and a confirmation message should be displayed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An error popped up at the bottom right.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The pop-up says: Something went wrong. Please try again later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify form submission with empty Name field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Leave the Name field empty.
+2. Fill in all other fields with valid data.
+3. Click the "Submit Now" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form should not submit, and an error message should appear indicating that the Name field is required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify form submission with invalid Email format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter an invalid email (e.g., "johndoe@com") in the Email field.
+2. Fill in all other fields with valid data.
+3. Click the "Submit Now" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form should not submit, and an error message should appear indicating that the email format is invalid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify form submission with empty Email field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Leave the Email field empty. 2. Fill in all other fields with valid data.
+3. Click the "Submit Now" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form should not submit, and an error message should appear indicating that the Email or Phone is required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form should not submit, and an error message should appear indicating that the Email or Phone is required is required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify form submission with invalid Phone Number format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter an invalid phone number (e.g., "12345") in the Phone Number field.
+2. Fill in all other fields with valid data.
+3. Click the "Submit Now" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form should not submit, and an error message should appear indicating that the phone number format is invalid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify form submission with empty Message field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Leave the Message field empty.
+2. Fill in all other fields with valid data.
+3. Click the "Submit Now" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form should not submit, and an error message should appear indicating that the Message field is required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify form submission with maximum character limit for Name field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter a name with more than the allowed character limit (e.g., 100 characters).
+2. Fill in all other fields with valid data.
+3. Click the "Submit Now" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form should not submit, and an error message should appear indicating that the Name field exceeds the character limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify form submission with maximum character limit for Message field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter a message with more than the allowed character limit (e.g., 1000 characters).
+2. Fill in all other fields with valid data.
+3. Click the "Submit Now" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form should not submit, and an error message should appear indicating that the Message field exceeds the character limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify form submission with a valid but very long Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter a valid but very long email (e.g., "a".repeat(100) + "@example.com").
+2. Fill in all other fields with valid data.
+3. Click the "Submit Now" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form should submit successfully if the email is valid, or an error message should appear if the email exceeds the allowed length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-0048</t>
+  </si>
+  <si>
     <t xml:space="preserve">TS-0002</t>
   </si>
   <si>
@@ -585,7 +770,7 @@
     <t xml:space="preserve">TS-0003</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Type (Load/Stress/Scalability)</t>
+    <t xml:space="preserve">Test Type</t>
   </si>
   <si>
     <t xml:space="preserve">Metrics to Measure</t>
@@ -595,6 +780,60 @@
   </si>
   <si>
     <t xml:space="preserve">Actual Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website should be accessible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page Load Time (ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load time ≤ 3 sec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Should be tested on Chrome, Firefox, and Edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JMeter configured with 100 virtual users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response Time (ms), Error Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response time &lt; 5 sec, Error rate &lt; 1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identify potential bottlenecks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scalability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JMeter set to ramp up users over 10 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server Throughput, Response Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Should handle 500 users with response time &lt; 6 sec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observe server behavior over time</t>
   </si>
   <si>
     <t xml:space="preserve">TS-0004</t>
@@ -634,7 +873,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -694,6 +933,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -743,7 +989,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -821,6 +1067,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -942,6 +1204,10 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -1226,15 +1492,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1048576"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="11.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="13.67"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="15.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="44.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="10.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="13.76"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="8" style="6" width="11.53"/>
   </cols>
   <sheetData>
@@ -1343,7 +1610,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
         <v>29</v>
       </c>
@@ -1445,8 +1712,11 @@
       <c r="F13" s="6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G13" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>51</v>
       </c>
@@ -1461,6 +1731,9 @@
       </c>
       <c r="F14" s="6" t="s">
         <v>44</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1497,7 +1770,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>61</v>
       </c>
@@ -1514,12 +1787,74 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A9:G23"/>
   <mergeCells count="12">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -1544,6 +1879,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1552,20 +1888,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:K27"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B1:L55"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="14.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="19.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="11.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="18.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="15.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="14.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="29.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="6" width="26.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="29.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="5" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="51.2"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="6" width="51.2"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="6" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1579,13 +1916,14 @@
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1595,10 +1933,11 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>22</v>
@@ -1611,10 +1950,11 @@
       <c r="I3" s="13"/>
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>26</v>
@@ -1627,13 +1967,14 @@
       <c r="I4" s="13"/>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -1643,6 +1984,7 @@
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="8"/>
@@ -1655,10 +1997,11 @@
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="14" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>32</v>
@@ -1667,33 +2010,36 @@
         <v>31</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>75</v>
+        <v>33</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>37</v>
@@ -1702,10 +2048,10 @@
         <v>35</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>38</v>
@@ -1714,15 +2060,18 @@
         <v>38</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>80</v>
+        <v>89</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>37</v>
@@ -1731,10 +2080,10 @@
         <v>35</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>38</v>
@@ -1743,15 +2092,18 @@
         <v>38</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>80</v>
+        <v>89</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>37</v>
@@ -1760,10 +2112,10 @@
         <v>35</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>38</v>
@@ -1772,15 +2124,18 @@
         <v>38</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>80</v>
+        <v>89</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>42</v>
@@ -1789,27 +2144,30 @@
         <v>40</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>90</v>
+        <v>97</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>91</v>
+        <v>100</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>42</v>
@@ -1818,30 +2176,33 @@
         <v>40</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>89</v>
+        <v>97</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>98</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>42</v>
@@ -1850,30 +2211,33 @@
         <v>40</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="G13" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="H13" s="16" t="s">
-        <v>89</v>
-      </c>
       <c r="I13" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>46</v>
@@ -1881,28 +2245,31 @@
       <c r="E14" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="16" t="s">
-        <v>101</v>
+      <c r="F14" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>80</v>
+        <v>89</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>46</v>
@@ -1910,28 +2277,31 @@
       <c r="E15" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="16" t="s">
-        <v>106</v>
+      <c r="F15" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>80</v>
+        <v>89</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>46</v>
@@ -1939,79 +2309,1356 @@
       <c r="E16" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G19" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G21" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>130</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>131</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>135</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>137</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>118</v>
+        <v>143</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B7:K27"/>
+  <autoFilter ref="B7:L55"/>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
@@ -2034,7 +3681,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:J1048576"/>
+  <dimension ref="B1:K7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.65"/>
@@ -2045,7 +3692,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="31.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="28.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="13.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="17" width="13.68"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2058,13 +3705,14 @@
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>119</v>
+        <v>204</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2073,10 +3721,11 @@
       <c r="H2" s="18"/>
       <c r="I2" s="18"/>
       <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>22</v>
@@ -2088,10 +3737,11 @@
       <c r="H3" s="18"/>
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>26</v>
@@ -2103,13 +3753,14 @@
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2118,6 +3769,7 @@
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18"/>
@@ -2129,52 +3781,42 @@
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>121</v>
+        <v>206</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>83</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B7:J7"/>
+  <autoFilter ref="B7:K7"/>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
@@ -2197,138 +3839,229 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:J1048576"/>
+  <dimension ref="B1:K10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="15.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="33.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="16.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="21.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="23.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="21.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="13.68"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="20" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="14.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="18.64"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="21.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="23.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="21.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="13.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="25.32"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="20" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B7" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>232</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B7:J7"/>
+  <autoFilter ref="B7:K7"/>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
@@ -2351,7 +4084,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:J1048576"/>
+  <dimension ref="B1:K7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.65"/>
@@ -2362,7 +4095,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="18.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="13.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="17" width="13.68"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2375,13 +4108,14 @@
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2390,10 +4124,11 @@
       <c r="H2" s="18"/>
       <c r="I2" s="18"/>
       <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>22</v>
@@ -2405,10 +4140,11 @@
       <c r="H3" s="18"/>
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>26</v>
@@ -2420,13 +4156,14 @@
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2435,6 +4172,7 @@
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18"/>
@@ -2446,46 +4184,42 @@
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>131</v>
+        <v>234</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>132</v>
+        <v>235</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>133</v>
+        <v>236</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>134</v>
+        <v>237</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>83</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B7:J7"/>
+  <autoFilter ref="B7:K7"/>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
@@ -2508,7 +4242,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:J1048576"/>
+  <dimension ref="B1:K7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.65"/>
@@ -2519,7 +4253,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="18.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="15.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="13.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="17" width="13.68"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2532,13 +4266,14 @@
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2547,10 +4282,11 @@
       <c r="H2" s="18"/>
       <c r="I2" s="18"/>
       <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>22</v>
@@ -2562,10 +4298,11 @@
       <c r="H3" s="18"/>
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>26</v>
@@ -2577,13 +4314,14 @@
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2592,6 +4330,7 @@
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18"/>
@@ -2603,43 +4342,42 @@
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>136</v>
+        <v>239</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>137</v>
+        <v>240</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>83</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B7:J7"/>
+  <autoFilter ref="B7:K7"/>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
@@ -2662,7 +4400,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:J1048576"/>
+  <dimension ref="B1:K7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.65"/>
@@ -2673,7 +4411,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="18.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="15.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="13.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="17" width="13.68"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2686,13 +4424,14 @@
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>138</v>
+        <v>241</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2701,10 +4440,11 @@
       <c r="H2" s="18"/>
       <c r="I2" s="18"/>
       <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>22</v>
@@ -2716,10 +4456,11 @@
       <c r="H3" s="18"/>
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>26</v>
@@ -2731,13 +4472,14 @@
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2746,6 +4488,7 @@
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="18"/>
@@ -2757,46 +4500,42 @@
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>139</v>
+        <v>242</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>83</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B7:J7"/>
+  <autoFilter ref="B7:K7"/>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>

--- a/Test_Files/TestSet-0001.xlsx
+++ b/Test_Files/TestSet-0001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Test Plan" sheetId="1" state="visible" r:id="rId3"/>
@@ -18,13 +18,13 @@
     <sheet name="Regression_Testing" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Compatibility_Testing!$B$7:$K$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Compatibility_Testing!$B$7:$K$14</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Functional_Testing!$B$7:$L$55</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Performance_Testing!$B$7:$K$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Performance_Testing!$B$7:$K$10</definedName>
     <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Regression_Testing!$B$7:$K$7</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Security_Testing!$B$7:$K$7</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Scenarios'!$A$9:$G$23</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">UI_UX_Testing!$B$7:$K$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">UI_UX_Testing!$B$7:$K$18</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="344">
   <si>
     <t xml:space="preserve">Test Plan</t>
   </si>
@@ -167,6 +167,9 @@
     <t xml:space="preserve">SC-0001</t>
   </si>
   <si>
+    <t xml:space="preserve">FSR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Landing</t>
   </si>
   <si>
@@ -236,43 +239,121 @@
     <t xml:space="preserve">SC-0007</t>
   </si>
   <si>
-    <t xml:space="preserve">Website should load within 3 seconds</t>
+    <t xml:space="preserve">Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure the time it takes for the website to fully load under normal network conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Determine how the website responds when a high number of concurrent users access the homepage.</t>
   </si>
   <si>
     <t xml:space="preserve">Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">SC-0008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input fields should reject SQL injection attempts</t>
-  </si>
-  <si>
     <t xml:space="preserve">SC-0009</t>
   </si>
   <si>
-    <t xml:space="preserve">Measure the time it takes for the website to fully load under normal network conditions.</t>
+    <t xml:space="preserve">Evaluate how well the website scales when traffic increases over time.</t>
   </si>
   <si>
     <t xml:space="preserve">SC-0010</t>
   </si>
   <si>
-    <t xml:space="preserve">Determine how the website responds when a high number of concurrent users access the homepage.</t>
+    <t xml:space="preserve">Verify that the website works correctly on Chrome, Firefox, Edge, and Safari.</t>
   </si>
   <si>
     <t xml:space="preserve">SC-0011</t>
   </si>
   <si>
-    <t xml:space="preserve">Evaluate how well the website scales when traffic increases over time.</t>
+    <t xml:space="preserve">Verify that the website is responsive and functional on desktop, tablet, and mobile devices.</t>
   </si>
   <si>
     <t xml:space="preserve">SC-0012</t>
   </si>
   <si>
+    <t xml:space="preserve">Verify that input fields are not vulnerable to SQL injection attacks.</t>
+  </si>
+  <si>
     <t xml:space="preserve">SC-0013</t>
   </si>
   <si>
+    <t xml:space="preserve">Verify that input fields are not vulnerable to XSS attacks.</t>
+  </si>
+  <si>
     <t xml:space="preserve">SC-0014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the application is protected against CSRF attacks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that sensitive data (e.g., passwords, tokens) is not exposed in requests or responses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that authentication mechanisms are secure and not vulnerable to brute force or session hijacking.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the application does not expose unnecessary information (e.g., server version, directory listings).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the layout is consistent across all pages and matches the Figma designs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the website is responsive and displays correctly on different screen sizes (desktop, tablet, mobile).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the fonts, font sizes, and typography are consistent with the Figma designs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the colors and themes used on the website match the Figma designs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that buttons and links are clickable and behave as expected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that images and icons are displayed correctly and are not broken or misaligned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that form fields are properly aligned and labeled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-0025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that error messages are displayed correctly and are user-friendly.</t>
   </si>
   <si>
     <t xml:space="preserve">Test Suite ID</t>
@@ -373,6 +454,9 @@
     <t xml:space="preserve">Fail</t>
   </si>
   <si>
+    <t xml:space="preserve">Error: A tree hydrated but some attributes of the server rendered HTML didn't match the client properties.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-0005</t>
   </si>
   <si>
@@ -384,9 +468,6 @@
   <si>
     <t xml:space="preserve">1. The chat client is displayed as an error
 2. Clicking on the chat client opens “Console Error”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: A tree hydrated but some attributes of the server rendered HTML didn't match the client properties.</t>
   </si>
   <si>
     <t xml:space="preserve">TC-0006</t>
@@ -633,7 +714,8 @@
     <t xml:space="preserve">Verify form submission with empty Email field</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Leave the Email field empty. 2. Fill in all other fields with valid data.
+    <t xml:space="preserve">1. Leave the Email field empty.
+2. Fill in all other fields with valid data.
 3. Click the "Submit Now" button.</t>
   </si>
   <si>
@@ -758,109 +840,368 @@
     <t xml:space="preserve">UI Element</t>
   </si>
   <si>
+    <t xml:space="preserve">Expected Appearance/Behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual Appearance / Behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the home page.
+2. Compare the header layout with Figma designs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header layout should match Figma designs (e.g., logo position, navigation menu alignment).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matched</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hero Section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the home page on desktop, tablet, and mobile.
+2. Check the hero section layout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hero section should be responsive and display correctly on all devices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact Page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form Fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the contact page.
+2. Check alignment of form fields and labels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form fields should be properly aligned, and labels should be clear and correctly positioned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit Button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the contact page.
+2. Click the "Submit Now" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Button should be clickable and trigger form submission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Images and Icons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the home page.
+2. Check all images and icons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Images and icons should be displayed correctly and not broken or misaligned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error Messages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the contact page.
+2. Enter invalid data in the fields and submit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the home page.
+2. Compare the footer layout with Figma designs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer layout should match Figma designs (e.g., links alignment, copyright text position).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Color Scheme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the contact page.
+2. Compare colors with Figma designs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colors should match Figma designs (e.g., button color, background color).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the home page.
+2. Click on each menu item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation menu should work correctly and redirect to the correct pages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the home page
+2. Scroll down to the client section area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client feedback area should be available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews failed to load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get started section should be available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get started area isn’t available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS-0003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metrics to Measure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website should be accessible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page Load Time (ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load time ≤ 3000ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Should be tested with Jmeter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JMeter configured with 100 virtual users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response Time (ms), Error Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Response time &lt; 5000ms
+2. Error rate &lt; 1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Avg. response time: 440ms
+2. Error rate: 0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scalability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JMeter set to ramp up users over 10 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server Throughput, Response Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Should handle 500 users with response time &lt; 6000ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Throughput: 1.2/sec
+Avg response time: 34205ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observe server behavior over time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS-0004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threat Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected Security Outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual Outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input Validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQL Injection (SQLi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Use OWASP ZAP to scan the contact form.
+2. Inject SQL queries into input fields.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application should reject SQL injection attempts and sanitize input.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skipped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-Site Scripting (XSS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Use OWASP ZAP to scan the contact form.
+2. Inject script tags into input fields.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application should reject XSS attempts and sanitize input.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-Site Request Forgery (CSRF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Use OWASP ZAP to check for CSRF tokens.
+2. Attempt to submit forms without a valid token.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application should reject requests without valid CSRF tokens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Protection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitive Data Exposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Use OWASP ZAP to scan requests/responses.
+2. Check for exposed sensitive data (e.g., passwords, tokens).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitive data should not be exposed in requests/responses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authentication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broken Authentication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Use OWASP ZAP to test login functionality.
+2. Attempt brute force attacks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application should block brute force attempts and enforce strong password policies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Misconfigurations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Use OWASP ZAP to scan for misconfigurations (e.g., directory listings, server info).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application should not expose unnecessary information (e.g., server version, directory listings).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS-0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Platform: Windows 10 Pro x64
+- Browser: MS Edge
+- Version: 133.0.3065.51 (Official build) (64-bit)
+- The contact page is open and loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Platform: Windows 10 Pro x64
+- Browser: Mozilla Firefox
+- Version: 135.0 (64-bit)
+- The contact page is open and loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Platform: Windows 10 Pro x64
+- Browser: Google Chrome
+- Version: 133.0.6943.60 (Official Build) (64-bit)
+- The contact page is open and loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homepage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Platform: Windows 10 Pro x64
+- Browser: MS Edge
+- Version: 133.0.3065.51 (Official build) (64-bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Platform: Windows 10 Pro x64
+- Browser: Mozilla Firefox
+- Version: 135.0 (64-bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Platform: Windows 10 Pro x64
+- Browser: Google Chrome
+- Version: 133.0.6943.60 (Official Build) (64-bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Platform: Samsung Galaxy S20 Ultra
+- Browser: Google Chrome
+- Version: 132.0.6834.165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Chrome on an Android device.
+2. Navigate to the Base URL.
+3. Check layout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website layout should be responsive and consistent with Figma designs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layout looks right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figma design not found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS-0006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Test Scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Appearance/Behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Appearance/Behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TS-0003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metrics to Measure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Performance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Performance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website should be accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page Load Time (ms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load time ≤ 3 sec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Should be tested on Chrome, Firefox, and Edge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JMeter configured with 100 virtual users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Response Time (ms), Error Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Response time &lt; 5 sec, Error rate &lt; 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identify potential bottlenecks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scalability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JMeter set to ramp up users over 10 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server Throughput, Response Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Should handle 500 users with response time &lt; 6 sec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observe server behavior over time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TS-0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Area (Authentication/Input Validation/etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threat Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Security Outcome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Outcome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TS-0005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform/OS/Device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TS-0006</t>
   </si>
   <si>
     <t xml:space="preserve">Previous Test Status</t>
@@ -873,7 +1214,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -927,19 +1268,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -989,7 +1317,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1019,6 +1347,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1038,6 +1370,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1054,12 +1390,8 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1067,22 +1399,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1492,7 +1808,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="11.26"/>
@@ -1501,156 +1817,160 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="15.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="44.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="10.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="13.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="13.75"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="8" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="7" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>35</v>
       </c>
+      <c r="B10" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="C10" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>3</v>
@@ -1658,19 +1978,22 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>3</v>
@@ -1678,19 +2001,22 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>3</v>
@@ -1698,19 +2024,22 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>9</v>
@@ -1718,19 +2047,22 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>30</v>
@@ -1738,121 +2070,466 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="D17" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>39</v>
+        <v>64</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>60</v>
+        <v>45</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G35" s="5" t="n">
+        <f aca="false">SUM(G10:G34)</f>
         <v>67</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E37" s="13"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E38" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="13"/>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A9:G23"/>
   <mergeCells count="12">
@@ -1897,7 +2574,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="15.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="14.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="29.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="6" width="26.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="29.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="26.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="29.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="5" width="9.64"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="11.53"/>
@@ -1905,1756 +2583,1759 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="6" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
+      <c r="B2" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
+      <c r="C5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="14" t="s">
+      <c r="B7" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K7" s="14" t="s">
+      <c r="E7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="K7" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="L7" s="14" t="s">
-        <v>84</v>
+      <c r="L7" s="16" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>35</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>35</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="17" t="s">
         <v>35</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>41</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>99</v>
+        <v>124</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>126</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>41</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>98</v>
+        <v>124</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>125</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>41</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>98</v>
+        <v>134</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>125</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="F14" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="15" t="s">
+      <c r="K16" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>96</v>
+      <c r="F17" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>102</v>
+      <c r="F18" s="17" t="s">
+        <v>130</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>106</v>
+      <c r="F19" s="17" t="s">
+        <v>133</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>96</v>
+      <c r="F20" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="H20" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="K20" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>102</v>
+      <c r="F21" s="17" t="s">
+        <v>130</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="H21" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="K21" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D22" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>106</v>
+      <c r="F22" s="17" t="s">
+        <v>133</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="H22" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="K22" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>96</v>
+      <c r="F23" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>102</v>
+      <c r="F24" s="17" t="s">
+        <v>130</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>106</v>
+      <c r="F25" s="17" t="s">
+        <v>133</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>139</v>
+        <v>54</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>144</v>
+        <v>54</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>146</v>
+        <v>54</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>139</v>
+        <v>54</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>144</v>
+        <v>54</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>146</v>
+        <v>54</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>139</v>
+        <v>54</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>144</v>
+        <v>54</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F34" s="16" t="s">
-        <v>146</v>
+        <v>54</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>139</v>
+        <v>54</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>144</v>
+        <v>54</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>146</v>
+        <v>54</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>139</v>
+        <v>54</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F39" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>144</v>
-      </c>
       <c r="G39" s="6" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>146</v>
+        <v>54</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="H40" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="I40" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L40" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L41" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="6" t="s">
+      <c r="G43" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="I43" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="6" t="s">
+      <c r="J43" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L43" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="6" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>139</v>
+        <v>54</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="6" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>144</v>
+        <v>54</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="6" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>146</v>
+        <v>54</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>139</v>
+        <v>54</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="6" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>144</v>
+        <v>54</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="6" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>146</v>
+        <v>54</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="6" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>139</v>
+        <v>54</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="6" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>144</v>
+        <v>54</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="6" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F52" s="16" t="s">
-        <v>146</v>
+        <v>54</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="6" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>139</v>
+        <v>54</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="6" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E54" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>144</v>
+        <v>54</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="6" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F55" s="16" t="s">
-        <v>146</v>
+        <v>54</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3681,142 +4362,463 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:K7"/>
+  <dimension ref="B1:K1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="15.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="13.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="15.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="13.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="31.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="28.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="17" width="13.68"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="14.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="15.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="13.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="18.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="6" width="31.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="19.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="6" width="13.68"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="6" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
+      <c r="B2" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
+      <c r="C5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="I7" s="19" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>84</v>
-      </c>
-    </row>
+      <c r="F8" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="B7:K7"/>
+  <autoFilter ref="B7:K18"/>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
@@ -3842,7 +4844,7 @@
   <dimension ref="B1:K10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="20" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="14.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="18.64"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="11.53"/>
@@ -3853,215 +4855,225 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="9.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="13.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="25.32"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="20" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="12" style="6" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="B2" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="C5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="21" t="s">
+      <c r="B7" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="14" t="s">
-        <v>84</v>
+      <c r="K7" s="16" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>220</v>
+      <c r="B8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="C9" s="22" t="s">
+      <c r="B9" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>232</v>
+      <c r="D10" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B7:K7"/>
+  <autoFilter ref="B7:K10"/>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
@@ -4084,138 +5096,313 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:K7"/>
+  <dimension ref="B1:K13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="49.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="15.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="14.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="13.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="18.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="17" width="13.68"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="14.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="25.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="17.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="14.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="6" width="31.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="18.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="6" width="13.68"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="6" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
+      <c r="B2" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
+      <c r="C5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="23" t="s">
+      <c r="B7" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="19" t="s">
-        <v>84</v>
+      <c r="K7" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4242,142 +5429,363 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:K7"/>
+  <dimension ref="B1:K14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="14.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="15.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="21.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="13.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="18.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="15.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="17" width="13.68"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="14.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="14.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="13.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="27.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="6" width="40.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="10.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="38.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="18" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="6" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
+      <c r="B2" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
+      <c r="C5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="23" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="19" t="s">
-        <v>84</v>
+      <c r="K7" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" s="6" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="18"/>
+    </row>
+    <row r="12" s="6" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="18"/>
+    </row>
+    <row r="13" s="6" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="18"/>
+    </row>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B7:K7"/>
+  <autoFilter ref="B7:K14"/>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
@@ -4403,135 +5811,135 @@
   <dimension ref="B1:K7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="11.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="15.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="21.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="13.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="18.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="15.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="17" width="13.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="14.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="11.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="15.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="13" width="21.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="13.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="13" width="18.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="13" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="13" width="13.68"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
+      <c r="B2" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
+      <c r="C5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="19" t="s">
+      <c r="B7" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="23" t="s">
+      <c r="D7" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="J7" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="19" t="s">
-        <v>84</v>
+      <c r="K7" s="20" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
